--- a/data/pack/us/gas_natural.xlsx
+++ b/data/pack/us/gas_natural.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1552"/>
+  <dimension ref="A1:K1553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -85794,6 +85794,61 @@
         </is>
       </c>
       <c r="K1552" t="inlineStr">
+        <is>
+          <t>Source: U.S. Energy Information Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>gas_natural</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>Gas natural (Henry Hub)</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E1553" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>mmbtu</t>
+        </is>
+      </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H1553" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1553" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration (Open Data API)</t>
+        </is>
+      </c>
+      <c r="J1553" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K1553" t="inlineStr">
         <is>
           <t>Source: U.S. Energy Information Administration</t>
         </is>
@@ -85893,7 +85948,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -85904,7 +85959,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="9">
@@ -85999,7 +86054,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>

--- a/data/pack/us/gas_natural.xlsx
+++ b/data/pack/us/gas_natural.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1553"/>
+  <dimension ref="A1:K1555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -85849,6 +85849,116 @@
         </is>
       </c>
       <c r="K1553" t="inlineStr">
+        <is>
+          <t>Source: U.S. Energy Information Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>gas_natural</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>Gas natural (Henry Hub)</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E1554" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>mmbtu</t>
+        </is>
+      </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H1554" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1554" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration (Open Data API)</t>
+        </is>
+      </c>
+      <c r="J1554" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K1554" t="inlineStr">
+        <is>
+          <t>Source: U.S. Energy Information Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>gas_natural</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>Gas natural (Henry Hub)</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E1555" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>mmbtu</t>
+        </is>
+      </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H1555" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1555" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration (Open Data API)</t>
+        </is>
+      </c>
+      <c r="J1555" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K1555" t="inlineStr">
         <is>
           <t>Source: U.S. Energy Information Administration</t>
         </is>
@@ -85948,7 +86058,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -85959,7 +86069,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1552</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="9">
@@ -86054,7 +86164,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/data/pack/us/gas_natural.xlsx
+++ b/data/pack/us/gas_natural.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1555"/>
+  <dimension ref="A1:K1556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -85927,11 +85927,11 @@
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E1555" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="F1555" t="inlineStr">
         <is>
@@ -85959,6 +85959,61 @@
         </is>
       </c>
       <c r="K1555" t="inlineStr">
+        <is>
+          <t>Source: U.S. Energy Information Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>gas_natural</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>Gas natural (Henry Hub)</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1556" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>mmbtu</t>
+        </is>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H1556" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1556" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration (Open Data API)</t>
+        </is>
+      </c>
+      <c r="J1556" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K1556" t="inlineStr">
         <is>
           <t>Source: U.S. Energy Information Administration</t>
         </is>
@@ -86058,7 +86113,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -86069,7 +86124,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="9">
@@ -86164,7 +86219,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
